--- a/output/260709__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260709__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일일정치주요뉴스" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="일일정치주요뉴스" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,16 +39,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000563C1"/>
-      <sz val="10"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -76,16 +66,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -482,12 +468,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>與, 이달 중 메가특구특별법 발의</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/mnews/article/016/0000000001</t>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
@@ -499,7 +480,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
@@ -513,7 +494,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
@@ -527,7 +508,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>

--- a/output/260709__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260709__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,16 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -66,12 +76,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -468,47 +482,112 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>(해당 시간대 기사 없음)</t>
+          <t>7월8일 모닝뉴스 헤드라인</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.radiokorea.com/news/article.php?uid=498847</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>조경태 "국힘 50%가 친윤…내란 옹호 세력 물갈이해야</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/018/0006325649?sid=100</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2) 더불어민주당 동정</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>[홍태화의 USA 인사이트] 앞으로 4년은 차기 대통령의 ‘외교 예습’ 기...</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/023/0003986521?sid=103</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>원 구성 공회전에도 민주당은 간다…'단독 국회' 본격 가동</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/119/0003109485?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>"재검표" 이구동성 외쳤지만...절차 두곤 '동상이몽'</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/052/0002376726?sid=100</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>[미리보는 이데일리 신문] 부모님 찬스 없으면 서울 전세도 못산다</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/mnews/article/018/0006325644?sid=101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2) 더불어민주당 동정</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>(해당 시간대 기사 없음)</t>
         </is>

--- a/output/260709__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260709__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>(기준: 2026-07-08 22:00 ~ 2026-07-09 08:00)</t>
+          <t>(기준: 2026-07-08 22:00 ~ 2026-07-09 06:00)</t>
         </is>
       </c>
     </row>
